--- a/output/sliding_window_results_window_7.xlsx
+++ b/output/sliding_window_results_window_7.xlsx
@@ -460,16 +460,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>31.38</v>
+        <v>41.5</v>
       </c>
       <c r="C2" t="n">
-        <v>29.21096462294038</v>
+        <v>42.04557534726577</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.169035377059622</v>
+        <v>0.5455753472657676</v>
       </c>
       <c r="E2" t="n">
-        <v>4.704714466936176</v>
+        <v>0.2976524595441629</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>32.28</v>
+        <v>43.7</v>
       </c>
       <c r="C3" t="n">
-        <v>30.87091265816404</v>
+        <v>48.05960290792583</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.409087341835964</v>
+        <v>4.359602907925826</v>
       </c>
       <c r="E3" t="n">
-        <v>1.985527136922342</v>
+        <v>19.00613751479532</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>33.1</v>
+        <v>48.1</v>
       </c>
       <c r="C4" t="n">
-        <v>31.9614024315945</v>
+        <v>53.62991975252643</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.138597568405501</v>
+        <v>5.529919752526425</v>
       </c>
       <c r="E4" t="n">
-        <v>1.29640442277892</v>
+        <v>30.58001246938192</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>34.4</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>33.26703244987812</v>
+        <v>59.34070631152108</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.132967550121876</v>
+        <v>6.340706311521082</v>
       </c>
       <c r="E5" t="n">
-        <v>1.283615469629165</v>
+        <v>40.20455652896328</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>36.3</v>
+        <v>56.1</v>
       </c>
       <c r="C6" t="n">
-        <v>34.49628624658651</v>
+        <v>63.43545661726901</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.803713753413483</v>
+        <v>7.33545661726901</v>
       </c>
       <c r="E6" t="n">
-        <v>3.253383304252954</v>
+        <v>53.8089237838357</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="C7" t="n">
-        <v>35.59917466894088</v>
+        <v>62.83838285341955</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.900825331059117</v>
+        <v>2.838382853419546</v>
       </c>
       <c r="E7" t="n">
-        <v>8.414787601314236</v>
+        <v>8.056417222586083</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>40.1</v>
+        <v>63.9</v>
       </c>
       <c r="C8" t="n">
-        <v>37.99920873652593</v>
+        <v>68.77201753921415</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.100791263474072</v>
+        <v>4.872017539214148</v>
       </c>
       <c r="E8" t="n">
-        <v>4.413323932688987</v>
+        <v>23.73655490241029</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>41.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>39.71722054748544</v>
+        <v>73.54641822285765</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.782779452514561</v>
+        <v>2.946418222857659</v>
       </c>
       <c r="E9" t="n">
-        <v>3.178302576308116</v>
+        <v>8.681380343987685</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>43.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99887272103697</v>
+        <v>84.47301699428039</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7011272789630354</v>
+        <v>3.57301699428038</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4915794613061101</v>
+        <v>12.7664504414164</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>48.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>43.9007849389311</v>
+        <v>85.62015674951471</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.199215061068905</v>
+        <v>-3.479843250485288</v>
       </c>
       <c r="E11" t="n">
-        <v>17.63340712910793</v>
+        <v>12.10930904794802</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C12" t="n">
-        <v>48.66852570511455</v>
+        <v>84.44100117763011</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.331474294885446</v>
+        <v>-10.55899882236989</v>
       </c>
       <c r="E12" t="n">
-        <v>18.76166956725337</v>
+        <v>111.4924561308086</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>56.1</v>
+        <v>98.8</v>
       </c>
       <c r="C13" t="n">
-        <v>53.74409462278157</v>
+        <v>96.63216277303445</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.355905377218427</v>
+        <v>-2.167837226965545</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5502901464067</v>
+        <v>4.699518242617666</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>60</v>
+        <v>103.3</v>
       </c>
       <c r="C14" t="n">
-        <v>57.50074693868428</v>
+        <v>98.21632410365299</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.49925306131572</v>
+        <v>-5.083675896347003</v>
       </c>
       <c r="E14" t="n">
-        <v>6.246265864495999</v>
+        <v>25.84376061909951</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>63.9</v>
+        <v>107</v>
       </c>
       <c r="C15" t="n">
-        <v>59.84227233141505</v>
+        <v>106.0878534914037</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.057727668584945</v>
+        <v>-0.9121465085962939</v>
       </c>
       <c r="E15" t="n">
-        <v>16.46515383239982</v>
+        <v>0.8320112531444088</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>70.59999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="C16" t="n">
-        <v>67.71747794164796</v>
+        <v>117.3380303801371</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.882522058352038</v>
+        <v>8.638030380137124</v>
       </c>
       <c r="E16" t="n">
-        <v>8.308933416886068</v>
+        <v>74.6155688481719</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>80.90000000000001</v>
+        <v>112.7</v>
       </c>
       <c r="C17" t="n">
-        <v>75.24044268973677</v>
+        <v>118.6186468408458</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.659557310263239</v>
+        <v>5.918646840845824</v>
       </c>
       <c r="E17" t="n">
-        <v>32.03058894815406</v>
+        <v>35.03038042665425</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>89.09999999999999</v>
+        <v>117.2</v>
       </c>
       <c r="C18" t="n">
-        <v>84.89373736265348</v>
+        <v>125.6670470445121</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.206262637346512</v>
+        <v>8.467047044512142</v>
       </c>
       <c r="E18" t="n">
-        <v>17.69264537433724</v>
+        <v>71.69088565398181</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>95</v>
+        <v>123.1</v>
       </c>
       <c r="C19" t="n">
-        <v>91.15288457015369</v>
+        <v>122.551759259761</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.847115429846312</v>
+        <v>-0.5482407402389526</v>
       </c>
       <c r="E19" t="n">
-        <v>14.80029713056157</v>
+        <v>0.3005679092577547</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>98.8</v>
+        <v>128.9</v>
       </c>
       <c r="C20" t="n">
-        <v>94.95868032466583</v>
+        <v>126.7455389686713</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.841319675334162</v>
+        <v>-2.154461031328736</v>
       </c>
       <c r="E20" t="n">
-        <v>14.75573684810935</v>
+        <v>4.641702335514083</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>103.3</v>
+        <v>135.1</v>
       </c>
       <c r="C21" t="n">
-        <v>97.57154319626318</v>
+        <v>148.2530412937334</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.728456803736819</v>
+        <v>13.15304129373339</v>
       </c>
       <c r="E21" t="n">
-        <v>32.81521735227865</v>
+        <v>173.0024952746559</v>
       </c>
     </row>
     <row r="22">
@@ -803,11 +803,11 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-58.74773429479976</v>
+        <v>49.61265862917662</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>214.0818439821278</v>
+        <v>711.3967414087748</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +820,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>10.70409219910639</v>
+        <v>35.56983707043874</v>
       </c>
     </row>
   </sheetData>
